--- a/py project/rocket/generated_data/initial_sets/rocket_initial_n80.xlsx
+++ b/py project/rocket/generated_data/initial_sets/rocket_initial_n80.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>头锥外形参数</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
@@ -499,35 +504,38 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>8.519786542305507</v>
       </c>
       <c r="I2" t="n">
-        <v>3.13</v>
+        <v>2.710192127815413</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>0.551769975038727</v>
       </c>
       <c r="K2" t="n">
-        <v>48.8</v>
+        <v>34.11477735174523</v>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>1.566173913255551</v>
       </c>
       <c r="M2" t="n">
-        <v>26.7</v>
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>120.4037251811</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +554,38 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.9</v>
+        <v>6.497490423710886</v>
       </c>
       <c r="I3" t="n">
-        <v>2.81</v>
+        <v>2.055676565141602</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1880616155071315</v>
       </c>
       <c r="K3" t="n">
-        <v>41.3</v>
+        <v>38.16782254950882</v>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>1.784792818173371</v>
       </c>
       <c r="M3" t="n">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>336.7731262813</v>
       </c>
     </row>
     <row r="4">
@@ -593,35 +604,38 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>12.65571415907051</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>4.732542044968112</v>
       </c>
       <c r="J4" t="n">
-        <v>0.63</v>
+        <v>0.8678486687141858</v>
       </c>
       <c r="K4" t="n">
-        <v>37.4</v>
+        <v>34.62245669909709</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.513464516211874</v>
       </c>
       <c r="M4" t="n">
-        <v>227</v>
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.594663601</v>
       </c>
     </row>
     <row r="5">
@@ -640,35 +654,38 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>18.20950641397419</v>
       </c>
       <c r="I5" t="n">
-        <v>3.97</v>
+        <v>4.744314564827842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1</v>
+        <v>0.7741609666566308</v>
       </c>
       <c r="K5" t="n">
-        <v>45.6</v>
+        <v>48.66960058135699</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.731443256886342</v>
       </c>
       <c r="M5" t="n">
-        <v>7.59</v>
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1960803558</v>
       </c>
     </row>
     <row r="6">
@@ -687,35 +704,38 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>18.94457079348051</v>
       </c>
       <c r="I6" t="n">
-        <v>4.17</v>
+        <v>4.081409565409796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.13</v>
+        <v>0.9372748893189851</v>
       </c>
       <c r="K6" t="n">
-        <v>33.9</v>
+        <v>45.0261417950596</v>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>1.912987128739565</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.0343458104</v>
       </c>
     </row>
     <row r="7">
@@ -734,35 +754,38 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18.7</v>
+        <v>3.109548446228053</v>
       </c>
       <c r="I7" t="n">
-        <v>4.81</v>
+        <v>2.715362511880268</v>
       </c>
       <c r="J7" t="n">
-        <v>0.86</v>
+        <v>0.5014872644153184</v>
       </c>
       <c r="K7" t="n">
-        <v>36.7</v>
+        <v>40.63069457115301</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.967050550752718</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>155.0460604276</v>
       </c>
     </row>
     <row r="8">
@@ -781,35 +804,38 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17.9</v>
+        <v>0.5997624471255181</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>2.219594065035777</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.9765222029412085</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>31.07583634878702</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.385195817782269</v>
       </c>
       <c r="M8" t="n">
-        <v>4.59</v>
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>212.1387695873</v>
       </c>
     </row>
     <row r="9">
@@ -828,35 +854,38 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>4.761202568367649</v>
       </c>
       <c r="I9" t="n">
-        <v>2.39</v>
+        <v>4.838403565668939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.83</v>
+        <v>0.3301825536955849</v>
       </c>
       <c r="K9" t="n">
-        <v>45.5</v>
+        <v>31.82829931328262</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.975121700356878</v>
       </c>
       <c r="M9" t="n">
-        <v>146</v>
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.5546602036</v>
       </c>
     </row>
     <row r="10">
@@ -875,35 +904,38 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>17.90466976385243</v>
       </c>
       <c r="I10" t="n">
-        <v>4.69</v>
+        <v>3.451344713831359</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>0.267583623871216</v>
       </c>
       <c r="K10" t="n">
-        <v>32.9</v>
+        <v>40.12983053713759</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.958328917550108</v>
       </c>
       <c r="M10" t="n">
-        <v>5.65</v>
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>33.0547013421</v>
       </c>
     </row>
     <row r="11">
@@ -922,35 +954,38 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.1</v>
+        <v>18.56986503506576</v>
       </c>
       <c r="I11" t="n">
-        <v>4.97</v>
+        <v>2.4555363379949</v>
       </c>
       <c r="J11" t="n">
-        <v>0.14</v>
+        <v>0.7075241522284512</v>
       </c>
       <c r="K11" t="n">
-        <v>44.2</v>
+        <v>32.03651607852261</v>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>1.626997462067809</v>
       </c>
       <c r="M11" t="n">
-        <v>0.64</v>
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>124.4789115549</v>
       </c>
     </row>
     <row r="12">
@@ -969,35 +1004,38 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>15.78007654001733</v>
       </c>
       <c r="I12" t="n">
-        <v>3.99</v>
+        <v>4.862575878410399</v>
       </c>
       <c r="J12" t="n">
-        <v>0.82</v>
+        <v>0.4043398163904721</v>
       </c>
       <c r="K12" t="n">
-        <v>40.6</v>
+        <v>49.97911392402589</v>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.886423622940882</v>
       </c>
       <c r="M12" t="n">
-        <v>7.19</v>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2415694545</v>
       </c>
     </row>
     <row r="13">
@@ -1016,35 +1054,38 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1.486406687628797</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>2.760121351136056</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.2428519021458099</v>
       </c>
       <c r="K13" t="n">
-        <v>42.6</v>
+        <v>43.62702310053504</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.618465715693413</v>
       </c>
       <c r="M13" t="n">
-        <v>6.25</v>
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>91.1870716392</v>
       </c>
     </row>
     <row r="14">
@@ -1063,35 +1104,38 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.3</v>
+        <v>7.764631863332863</v>
       </c>
       <c r="I14" t="n">
-        <v>4.63</v>
+        <v>3.663081301890197</v>
       </c>
       <c r="J14" t="n">
-        <v>0.91</v>
+        <v>0.03200058629413199</v>
       </c>
       <c r="K14" t="n">
-        <v>43.3</v>
+        <v>35.48262182809572</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>1.669543162583343</v>
       </c>
       <c r="M14" t="n">
-        <v>0.27</v>
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33.2943568383</v>
       </c>
     </row>
     <row r="15">
@@ -1110,35 +1154,38 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.2</v>
+        <v>11.60740105806106</v>
       </c>
       <c r="I15" t="n">
-        <v>3.71</v>
+        <v>2.954760018906254</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32</v>
+        <v>0.1346558551370383</v>
       </c>
       <c r="K15" t="n">
-        <v>33.5</v>
+        <v>43.01853757831577</v>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>1.013647843793634</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>41.4976190354</v>
       </c>
     </row>
     <row r="16">
@@ -1157,35 +1204,38 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>6.117219309624726</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.849102255117048</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.3823960096366186</v>
       </c>
       <c r="K16" t="n">
-        <v>35.8</v>
+        <v>43.9073391801076</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>1.308014681326528</v>
       </c>
       <c r="M16" t="n">
-        <v>24.6</v>
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.2015625857</v>
       </c>
     </row>
     <row r="17">
@@ -1204,35 +1254,38 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.6</v>
+        <v>13.69779996761362</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>3.835356246473322</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>0.3473382478640678</v>
       </c>
       <c r="K17" t="n">
-        <v>47.4</v>
+        <v>35.51227714584459</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.221561260224345</v>
       </c>
       <c r="M17" t="n">
-        <v>77.59999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.5741738054</v>
       </c>
     </row>
     <row r="18">
@@ -1251,35 +1304,38 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.5</v>
+        <v>14.66196923680304</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>3.572029402692908</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44</v>
+        <v>0.9126291769294704</v>
       </c>
       <c r="K18" t="n">
-        <v>31.5</v>
+        <v>41.40507610314028</v>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.988041290837492</v>
       </c>
       <c r="M18" t="n">
-        <v>73.3</v>
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>18.1103816424</v>
       </c>
     </row>
     <row r="19">
@@ -1298,35 +1354,38 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>19.04133866857839</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>4.030244911638306</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.390392586268072</v>
       </c>
       <c r="K19" t="n">
-        <v>44.6</v>
+        <v>30.48927584506934</v>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.12958752626522</v>
       </c>
       <c r="M19" t="n">
-        <v>25.9</v>
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12.5043961238</v>
       </c>
     </row>
     <row r="20">
@@ -1345,35 +1404,38 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>15.34132205328829</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>4.670318238673206</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.5291856042169948</v>
       </c>
       <c r="K20" t="n">
-        <v>49.5</v>
+        <v>37.08945741688711</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.442042479112834</v>
       </c>
       <c r="M20" t="n">
-        <v>159</v>
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.4368689177</v>
       </c>
     </row>
     <row r="21">
@@ -1392,35 +1454,38 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>1.55125709717328</v>
       </c>
       <c r="I21" t="n">
-        <v>4.13</v>
+        <v>2.240236142211938</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.03909739748766215</v>
       </c>
       <c r="K21" t="n">
-        <v>36.1</v>
+        <v>42.58271499266665</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.088004384665715</v>
       </c>
       <c r="M21" t="n">
-        <v>11.8</v>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>143.5398721285</v>
       </c>
     </row>
     <row r="22">
@@ -1439,35 +1504,38 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>9.35162749557168</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>2.616304026049294</v>
       </c>
       <c r="J22" t="n">
-        <v>0.84</v>
+        <v>0.8100525580376734</v>
       </c>
       <c r="K22" t="n">
-        <v>42</v>
+        <v>46.46888519254929</v>
       </c>
       <c r="L22" t="n">
-        <v>1.74</v>
+        <v>1.868875909240681</v>
       </c>
       <c r="M22" t="n">
-        <v>17.3</v>
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>126.3518185079</v>
       </c>
     </row>
     <row r="23">
@@ -1486,35 +1554,38 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.6</v>
+        <v>12.43391786926482</v>
       </c>
       <c r="I23" t="n">
-        <v>3.58</v>
+        <v>4.20632625688801</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.8960165023096367</v>
       </c>
       <c r="K23" t="n">
-        <v>37.9</v>
+        <v>37.44726264089912</v>
       </c>
       <c r="L23" t="n">
-        <v>1.06</v>
+        <v>1.153645337068844</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.101100871</v>
       </c>
     </row>
     <row r="24">
@@ -1533,35 +1604,38 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>9.95631771149894</v>
       </c>
       <c r="I24" t="n">
-        <v>2.01</v>
+        <v>4.281598924819553</v>
       </c>
       <c r="J24" t="n">
-        <v>0.76</v>
+        <v>0.567533866045062</v>
       </c>
       <c r="K24" t="n">
-        <v>47.8</v>
+        <v>36.69086885383214</v>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>1.477533175665441</v>
       </c>
       <c r="M24" t="n">
-        <v>306</v>
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7.5272146827</v>
       </c>
     </row>
     <row r="25">
@@ -1580,35 +1654,38 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.4</v>
+        <v>4.69783733127998</v>
       </c>
       <c r="I25" t="n">
-        <v>2.35</v>
+        <v>3.474797444809447</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.1515964941834195</v>
       </c>
       <c r="K25" t="n">
-        <v>39.8</v>
+        <v>46.00439500173992</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.537511255480929</v>
       </c>
       <c r="M25" t="n">
-        <v>139</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21.9036013994</v>
       </c>
     </row>
     <row r="26">
@@ -1627,35 +1704,38 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8.699999999999999</v>
+        <v>14.02576127488338</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>3.057129969701387</v>
       </c>
       <c r="J26" t="n">
-        <v>0.54</v>
+        <v>0.6719210702975608</v>
       </c>
       <c r="K26" t="n">
-        <v>40.2</v>
+        <v>48.95375643530251</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03</v>
+        <v>1.358889440712508</v>
       </c>
       <c r="M26" t="n">
-        <v>147</v>
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>22.9810406584</v>
       </c>
     </row>
     <row r="27">
@@ -1674,35 +1754,38 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.9</v>
+        <v>3.303407385213267</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>4.401430314239871</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02</v>
+        <v>0.8794837720460595</v>
       </c>
       <c r="K27" t="n">
-        <v>38.4</v>
+        <v>44.06899656703943</v>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>1.41480069725278</v>
       </c>
       <c r="M27" t="n">
-        <v>262</v>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.9291999696</v>
       </c>
     </row>
     <row r="28">
@@ -1721,35 +1804,38 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.2</v>
+        <v>7.135380677544932</v>
       </c>
       <c r="I28" t="n">
-        <v>2.91</v>
+        <v>4.986207474927348</v>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>0.003526463782659266</v>
       </c>
       <c r="K28" t="n">
-        <v>38.6</v>
+        <v>42.42802246511008</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>1.139476736925185</v>
       </c>
       <c r="M28" t="n">
-        <v>87.5</v>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.4576065379</v>
       </c>
     </row>
     <row r="29">
@@ -1768,35 +1854,38 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16.6</v>
+        <v>14.36124168581024</v>
       </c>
       <c r="I29" t="n">
-        <v>2.71</v>
+        <v>4.308513845010092</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.2753104213577691</v>
       </c>
       <c r="K29" t="n">
-        <v>40.9</v>
+        <v>45.59636388916521</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.067125430634992</v>
       </c>
       <c r="M29" t="n">
-        <v>50.5</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.5277147697</v>
       </c>
     </row>
     <row r="30">
@@ -1815,35 +1904,38 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.2</v>
+        <v>1.111679821228768</v>
       </c>
       <c r="I30" t="n">
-        <v>3.32</v>
+        <v>4.373814059993499</v>
       </c>
       <c r="J30" t="n">
-        <v>0.44</v>
+        <v>0.5881209084777707</v>
       </c>
       <c r="K30" t="n">
-        <v>30.8</v>
+        <v>32.32758834844555</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.02773349920052</v>
       </c>
       <c r="M30" t="n">
-        <v>33.6</v>
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10.3235342536</v>
       </c>
     </row>
     <row r="31">
@@ -1862,35 +1954,38 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>3.765557304493783</v>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>2.435747120043652</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.1788761389446488</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>49.02011908339972</v>
       </c>
       <c r="L31" t="n">
-        <v>1.54</v>
+        <v>1.170766214037984</v>
       </c>
       <c r="M31" t="n">
-        <v>9.25</v>
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>93.3899714854</v>
       </c>
     </row>
     <row r="32">
@@ -1909,35 +2004,38 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>12.5</v>
+        <v>2.283384938076783</v>
       </c>
       <c r="I32" t="n">
-        <v>4.35</v>
+        <v>4.122501081899319</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3</v>
+        <v>0.1627402356163092</v>
       </c>
       <c r="K32" t="n">
-        <v>44.9</v>
+        <v>41.99028188196858</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.89226918030401</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>11.6760706185</v>
       </c>
     </row>
     <row r="33">
@@ -1956,35 +2054,38 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>7.460085389478104</v>
       </c>
       <c r="I33" t="n">
-        <v>3.65</v>
+        <v>3.029214772649754</v>
       </c>
       <c r="J33" t="n">
-        <v>0.62</v>
+        <v>0.9636504436192996</v>
       </c>
       <c r="K33" t="n">
-        <v>35.2</v>
+        <v>33.38022494750047</v>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>1.260353912973117</v>
       </c>
       <c r="M33" t="n">
-        <v>25.5</v>
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>62.4357956212</v>
       </c>
     </row>
     <row r="34">
@@ -2003,35 +2104,38 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>12.78254274046618</v>
       </c>
       <c r="I34" t="n">
-        <v>3.07</v>
+        <v>2.933562807971519</v>
       </c>
       <c r="J34" t="n">
-        <v>0.38</v>
+        <v>0.6990628995244607</v>
       </c>
       <c r="K34" t="n">
-        <v>42.3</v>
+        <v>33.84667978856439</v>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>1.329458857392244</v>
       </c>
       <c r="M34" t="n">
-        <v>79.2</v>
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>55.2001297315</v>
       </c>
     </row>
     <row r="35">
@@ -2050,35 +2154,38 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.1</v>
+        <v>16.02101373046481</v>
       </c>
       <c r="I35" t="n">
-        <v>3.26</v>
+        <v>3.29219929485152</v>
       </c>
       <c r="J35" t="n">
-        <v>0.46</v>
+        <v>0.7135917170548971</v>
       </c>
       <c r="K35" t="n">
-        <v>35.5</v>
+        <v>47.42117323009192</v>
       </c>
       <c r="L35" t="n">
-        <v>1.83</v>
+        <v>1.680619946905326</v>
       </c>
       <c r="M35" t="n">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>18.6623258466</v>
       </c>
     </row>
     <row r="36">
@@ -2097,35 +2204,38 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.3</v>
+        <v>1.828072527082882</v>
       </c>
       <c r="I36" t="n">
-        <v>4.74</v>
+        <v>2.114432217307364</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>0.4669267684226489</v>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>47.09475642651476</v>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>1.491170115063198</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>216.2777530747</v>
       </c>
     </row>
     <row r="37">
@@ -2144,35 +2254,38 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>13.9</v>
+        <v>13.32912268642549</v>
       </c>
       <c r="I37" t="n">
-        <v>4.05</v>
+        <v>3.418225841569172</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06</v>
+        <v>0.8150600064881794</v>
       </c>
       <c r="K37" t="n">
-        <v>30.7</v>
+        <v>38.56988257487605</v>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.595776013324518</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>21.7250994003</v>
       </c>
     </row>
     <row r="38">
@@ -2191,35 +2304,38 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>16.3</v>
+        <v>16.9417040394654</v>
       </c>
       <c r="I38" t="n">
-        <v>4.32</v>
+        <v>2.268540816792069</v>
       </c>
       <c r="J38" t="n">
-        <v>0.37</v>
+        <v>0.6094427553815028</v>
       </c>
       <c r="K38" t="n">
-        <v>34.3</v>
+        <v>43.34732858466438</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.212149052464858</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>100.7205212363</v>
       </c>
     </row>
     <row r="39">
@@ -2238,35 +2354,38 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>13.18350438640609</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.49560463633067</v>
       </c>
       <c r="J39" t="n">
-        <v>0.21</v>
+        <v>0.939511051035949</v>
       </c>
       <c r="K39" t="n">
-        <v>37.2</v>
+        <v>42.18664564019016</v>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>1.748238460774927</v>
       </c>
       <c r="M39" t="n">
-        <v>2.72</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>116.6288468345</v>
       </c>
     </row>
     <row r="40">
@@ -2285,35 +2404,38 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.7</v>
+        <v>0.1136387451197274</v>
       </c>
       <c r="I40" t="n">
-        <v>4.85</v>
+        <v>4.574182195293871</v>
       </c>
       <c r="J40" t="n">
-        <v>0.34</v>
+        <v>0.4377995418685513</v>
       </c>
       <c r="K40" t="n">
-        <v>42.9</v>
+        <v>45.37921358557604</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.396318573210273</v>
       </c>
       <c r="M40" t="n">
-        <v>0.793</v>
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.4575322525</v>
       </c>
     </row>
     <row r="41">
@@ -2332,35 +2454,38 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.4</v>
+        <v>10.1677712089802</v>
       </c>
       <c r="I41" t="n">
-        <v>2.74</v>
+        <v>3.153565055270769</v>
       </c>
       <c r="J41" t="n">
-        <v>0.92</v>
+        <v>0.6144218299518647</v>
       </c>
       <c r="K41" t="n">
-        <v>46.3</v>
+        <v>44.76922984828181</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>1.452166547475741</v>
       </c>
       <c r="M41" t="n">
-        <v>29.5</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>28.8828381273</v>
       </c>
     </row>
     <row r="42">
@@ -2379,35 +2504,38 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9.9</v>
+        <v>10.88964004244164</v>
       </c>
       <c r="I42" t="n">
-        <v>2.61</v>
+        <v>3.611540255546598</v>
       </c>
       <c r="J42" t="n">
-        <v>0.52</v>
+        <v>0.750927167974144</v>
       </c>
       <c r="K42" t="n">
-        <v>32.8</v>
+        <v>39.40265737833635</v>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.551152073258975</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>16.8938139084</v>
       </c>
     </row>
     <row r="43">
@@ -2426,35 +2554,38 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>10.42318947991848</v>
       </c>
       <c r="I43" t="n">
-        <v>4.54</v>
+        <v>3.887912416873008</v>
       </c>
       <c r="J43" t="n">
-        <v>0.28</v>
+        <v>0.6284370147303363</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>30.61019380557942</v>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>1.043722217227784</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16.5252571914</v>
       </c>
     </row>
     <row r="44">
@@ -2473,35 +2604,38 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7.7</v>
+        <v>3.692941517020356</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>2.36220329429391</v>
       </c>
       <c r="J44" t="n">
-        <v>0.77</v>
+        <v>0.4549706772627585</v>
       </c>
       <c r="K44" t="n">
-        <v>49.7</v>
+        <v>44.30517206539663</v>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>1.642705190034276</v>
       </c>
       <c r="M44" t="n">
-        <v>20.1</v>
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>181.3071687141</v>
       </c>
     </row>
     <row r="45">
@@ -2520,35 +2654,38 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>19.7</v>
+        <v>19.58429304965504</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>2.104297685023305</v>
       </c>
       <c r="J45" t="n">
-        <v>0.97</v>
+        <v>0.6476502152394372</v>
       </c>
       <c r="K45" t="n">
-        <v>39.5</v>
+        <v>41.54178910643495</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.466553594345656</v>
       </c>
       <c r="M45" t="n">
-        <v>59.8</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>160.7486545302</v>
       </c>
     </row>
     <row r="46">
@@ -2567,35 +2704,38 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.8</v>
+        <v>8.045242812260522</v>
       </c>
       <c r="I46" t="n">
-        <v>2.47</v>
+        <v>4.618224284767409</v>
       </c>
       <c r="J46" t="n">
-        <v>0.16</v>
+        <v>0.7947583775342151</v>
       </c>
       <c r="K46" t="n">
-        <v>43.9</v>
+        <v>48.25398410085353</v>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.341135294929445</v>
       </c>
       <c r="M46" t="n">
-        <v>149</v>
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.4621414634</v>
       </c>
     </row>
     <row r="47">
@@ -2614,35 +2754,38 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>19.75824858038048</v>
       </c>
       <c r="I47" t="n">
-        <v>3.36</v>
+        <v>4.960960666168591</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6</v>
+        <v>0.958000878365179</v>
       </c>
       <c r="K47" t="n">
-        <v>49</v>
+        <v>40.29642009495417</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.702215453917329</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.200506872</v>
       </c>
     </row>
     <row r="48">
@@ -2661,35 +2804,38 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.9</v>
+        <v>2.159362342178083</v>
       </c>
       <c r="I48" t="n">
-        <v>3.87</v>
+        <v>3.792632226721197</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.3051656740101838</v>
       </c>
       <c r="K48" t="n">
-        <v>32.4</v>
+        <v>30.80102541255535</v>
       </c>
       <c r="L48" t="n">
-        <v>1.29</v>
+        <v>1.411760454267165</v>
       </c>
       <c r="M48" t="n">
-        <v>21.5</v>
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>30.9598534224</v>
       </c>
     </row>
     <row r="49">
@@ -2708,35 +2854,38 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>0.7754835246418186</v>
       </c>
       <c r="I49" t="n">
-        <v>4.45</v>
+        <v>2.815354194883349</v>
       </c>
       <c r="J49" t="n">
-        <v>0.71</v>
+        <v>0.3227562598593141</v>
       </c>
       <c r="K49" t="n">
-        <v>48.3</v>
+        <v>37.50621648133666</v>
       </c>
       <c r="L49" t="n">
-        <v>1.26</v>
+        <v>1.857297630061378</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>118.5485454425</v>
       </c>
     </row>
     <row r="50">
@@ -2755,35 +2904,38 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>14.7</v>
+        <v>8.399604764570308</v>
       </c>
       <c r="I50" t="n">
-        <v>4.26</v>
+        <v>3.100958968437119</v>
       </c>
       <c r="J50" t="n">
-        <v>0.73</v>
+        <v>0.3557359564335129</v>
       </c>
       <c r="K50" t="n">
-        <v>46.5</v>
+        <v>31.34124569966837</v>
       </c>
       <c r="L50" t="n">
-        <v>1.06</v>
+        <v>1.577100125529493</v>
       </c>
       <c r="M50" t="n">
-        <v>0.777</v>
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>80.0501166241</v>
       </c>
     </row>
     <row r="51">
@@ -2802,35 +2954,38 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12.3</v>
+        <v>12.18451353756261</v>
       </c>
       <c r="I51" t="n">
-        <v>2.87</v>
+        <v>2.011942419852704</v>
       </c>
       <c r="J51" t="n">
-        <v>0.41</v>
+        <v>0.1097421781359784</v>
       </c>
       <c r="K51" t="n">
-        <v>34.5</v>
+        <v>42.97999756287799</v>
       </c>
       <c r="L51" t="n">
-        <v>1.63</v>
+        <v>1.527701173867338</v>
       </c>
       <c r="M51" t="n">
-        <v>84.3</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>270.3426047817</v>
       </c>
     </row>
     <row r="52">
@@ -2849,35 +3004,38 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.4</v>
+        <v>17.54825793304782</v>
       </c>
       <c r="I52" t="n">
-        <v>4.31</v>
+        <v>4.491659650419322</v>
       </c>
       <c r="J52" t="n">
-        <v>0.73</v>
+        <v>0.7810202217334523</v>
       </c>
       <c r="K52" t="n">
-        <v>44.6</v>
+        <v>35.82165525500182</v>
       </c>
       <c r="L52" t="n">
-        <v>1.16</v>
+        <v>1.789574250711256</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.7293401388</v>
       </c>
     </row>
     <row r="53">
@@ -2896,35 +3054,38 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.3</v>
+        <v>15.00357505110419</v>
       </c>
       <c r="I53" t="n">
-        <v>2.26</v>
+        <v>4.629537804981854</v>
       </c>
       <c r="J53" t="n">
-        <v>0.63</v>
+        <v>0.5423399313648891</v>
       </c>
       <c r="K53" t="n">
-        <v>47.4</v>
+        <v>39.79798476383856</v>
       </c>
       <c r="L53" t="n">
-        <v>1.1</v>
+        <v>1.765183118275984</v>
       </c>
       <c r="M53" t="n">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.5087365726</v>
       </c>
     </row>
     <row r="54">
@@ -2943,35 +3104,38 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.4</v>
+        <v>15.54791827854889</v>
       </c>
       <c r="I54" t="n">
-        <v>4.41</v>
+        <v>3.259542475069582</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.01622759768963811</v>
       </c>
       <c r="K54" t="n">
-        <v>34.9</v>
+        <v>36.18036355566045</v>
       </c>
       <c r="L54" t="n">
-        <v>1.76</v>
+        <v>1.189838715752522</v>
       </c>
       <c r="M54" t="n">
-        <v>4.56</v>
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>44.9085088906</v>
       </c>
     </row>
     <row r="55">
@@ -2990,35 +3154,38 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>19.5</v>
+        <v>17.40781834339159</v>
       </c>
       <c r="I55" t="n">
-        <v>3.91</v>
+        <v>2.540763468567527</v>
       </c>
       <c r="J55" t="n">
-        <v>0.26</v>
+        <v>0.8552426069639318</v>
       </c>
       <c r="K55" t="n">
-        <v>49.4</v>
+        <v>30.18369594661068</v>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>1.23092056646102</v>
       </c>
       <c r="M55" t="n">
-        <v>1.06</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>90.3723298396</v>
       </c>
     </row>
     <row r="56">
@@ -3037,35 +3204,38 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.1</v>
+        <v>0.4501686396187414</v>
       </c>
       <c r="I56" t="n">
-        <v>2.54</v>
+        <v>3.192339964616321</v>
       </c>
       <c r="J56" t="n">
-        <v>0.85</v>
+        <v>0.990264232710742</v>
       </c>
       <c r="K56" t="n">
-        <v>31.8</v>
+        <v>46.67220798942256</v>
       </c>
       <c r="L56" t="n">
-        <v>1.51</v>
+        <v>1.279347195624464</v>
       </c>
       <c r="M56" t="n">
-        <v>166</v>
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>29.4740332706</v>
       </c>
     </row>
     <row r="57">
@@ -3084,35 +3254,38 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>6.7</v>
+        <v>11.05787319608046</v>
       </c>
       <c r="I57" t="n">
-        <v>2.96</v>
+        <v>2.669072425225911</v>
       </c>
       <c r="J57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1162678822113209</v>
       </c>
       <c r="K57" t="n">
-        <v>41.3</v>
+        <v>36.94908779944378</v>
       </c>
       <c r="L57" t="n">
-        <v>1.28</v>
+        <v>1.801387811233828</v>
       </c>
       <c r="M57" t="n">
-        <v>56.2</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>152.4068075547</v>
       </c>
     </row>
     <row r="58">
@@ -3131,35 +3304,38 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16</v>
+        <v>9.718908419222068</v>
       </c>
       <c r="I58" t="n">
-        <v>3.67</v>
+        <v>3.233955782406215</v>
       </c>
       <c r="J58" t="n">
-        <v>0.35</v>
+        <v>0.725475905474571</v>
       </c>
       <c r="K58" t="n">
-        <v>37</v>
+        <v>46.77950016024694</v>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>1.836226983497052</v>
       </c>
       <c r="M58" t="n">
-        <v>18.3</v>
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>35.4196234654</v>
       </c>
     </row>
     <row r="59">
@@ -3178,35 +3354,38 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>10.4</v>
+        <v>6.977162263499959</v>
       </c>
       <c r="I59" t="n">
-        <v>4.84</v>
+        <v>4.513675255341384</v>
       </c>
       <c r="J59" t="n">
-        <v>0.54</v>
+        <v>0.2238534510385011</v>
       </c>
       <c r="K59" t="n">
-        <v>43.6</v>
+        <v>36.27293634453554</v>
       </c>
       <c r="L59" t="n">
-        <v>1.36</v>
+        <v>1.713973759344381</v>
       </c>
       <c r="M59" t="n">
-        <v>0.391</v>
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7.2335945548</v>
       </c>
     </row>
     <row r="60">
@@ -3225,35 +3404,38 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.6</v>
+        <v>11.94503370883996</v>
       </c>
       <c r="I60" t="n">
-        <v>2.67</v>
+        <v>3.756825332179337</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1</v>
+        <v>0.2877341117044961</v>
       </c>
       <c r="K60" t="n">
-        <v>39.1</v>
+        <v>39.0823691425911</v>
       </c>
       <c r="L60" t="n">
-        <v>1.97</v>
+        <v>1.940648749736881</v>
       </c>
       <c r="M60" t="n">
-        <v>179</v>
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>22.4665861529</v>
       </c>
     </row>
     <row r="61">
@@ -3272,35 +3454,38 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.5</v>
+        <v>9.185466936844632</v>
       </c>
       <c r="I61" t="n">
-        <v>3.42</v>
+        <v>4.146236285457856</v>
       </c>
       <c r="J61" t="n">
-        <v>0.45</v>
+        <v>0.4143369023037634</v>
       </c>
       <c r="K61" t="n">
-        <v>32</v>
+        <v>34.46783875866675</v>
       </c>
       <c r="L61" t="n">
-        <v>1.64</v>
+        <v>1.92928378012444</v>
       </c>
       <c r="M61" t="n">
-        <v>37.3</v>
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>16.8204257885</v>
       </c>
     </row>
     <row r="62">
@@ -3319,35 +3504,38 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>4.030093123852708</v>
       </c>
       <c r="I62" t="n">
-        <v>3.63</v>
+        <v>4.796203307658084</v>
       </c>
       <c r="J62" t="n">
-        <v>0.06</v>
+        <v>0.0588983070241066</v>
       </c>
       <c r="K62" t="n">
-        <v>42.2</v>
+        <v>49.48111296362437</v>
       </c>
       <c r="L62" t="n">
-        <v>1.02</v>
+        <v>1.299139153600534</v>
       </c>
       <c r="M62" t="n">
-        <v>16.1</v>
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.3275598601</v>
       </c>
     </row>
     <row r="63">
@@ -3366,35 +3554,38 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14.4</v>
+        <v>18.40371078225757</v>
       </c>
       <c r="I63" t="n">
-        <v>2.93</v>
+        <v>3.342367549426606</v>
       </c>
       <c r="J63" t="n">
-        <v>0.29</v>
+        <v>0.580083882778488</v>
       </c>
       <c r="K63" t="n">
-        <v>31.7</v>
+        <v>32.52484319672899</v>
       </c>
       <c r="L63" t="n">
-        <v>1.73</v>
+        <v>1.6932320125177</v>
       </c>
       <c r="M63" t="n">
-        <v>96.09999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>33.3083727135</v>
       </c>
     </row>
     <row r="64">
@@ -3413,35 +3604,38 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.2</v>
+        <v>2.569992605891214</v>
       </c>
       <c r="I64" t="n">
-        <v>3.65</v>
+        <v>4.329627719977511</v>
       </c>
       <c r="J64" t="n">
-        <v>0.45</v>
+        <v>0.514259550231373</v>
       </c>
       <c r="K64" t="n">
-        <v>30.1</v>
+        <v>31.73990589391441</v>
       </c>
       <c r="L64" t="n">
-        <v>1.19</v>
+        <v>1.055863797884486</v>
       </c>
       <c r="M64" t="n">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>11.4954932573</v>
       </c>
     </row>
     <row r="65">
@@ -3460,35 +3654,38 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>9.699999999999999</v>
+        <v>14.78948107162886</v>
       </c>
       <c r="I65" t="n">
-        <v>2.28</v>
+        <v>2.174940644663674</v>
       </c>
       <c r="J65" t="n">
-        <v>0.77</v>
+        <v>0.9106608864771291</v>
       </c>
       <c r="K65" t="n">
-        <v>39.2</v>
+        <v>38.35119279573777</v>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>1.60706356169046</v>
       </c>
       <c r="M65" t="n">
-        <v>239</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>187.6715461865</v>
       </c>
     </row>
     <row r="66">
@@ -3507,35 +3704,38 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.5</v>
+        <v>19.39160070199818</v>
       </c>
       <c r="I66" t="n">
-        <v>4.45</v>
+        <v>4.907619638361679</v>
       </c>
       <c r="J66" t="n">
-        <v>0.87</v>
+        <v>0.4360456106016583</v>
       </c>
       <c r="K66" t="n">
-        <v>48.8</v>
+        <v>40.85296128189268</v>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>1.007345382625362</v>
       </c>
       <c r="M66" t="n">
-        <v>1.65</v>
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.2783877036</v>
       </c>
     </row>
     <row r="67">
@@ -3554,35 +3754,38 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>11</v>
+        <v>7.502031027396178</v>
       </c>
       <c r="I67" t="n">
-        <v>4.83</v>
+        <v>2.89743731623106</v>
       </c>
       <c r="J67" t="n">
-        <v>0.13</v>
+        <v>0.2304317581910928</v>
       </c>
       <c r="K67" t="n">
-        <v>32.1</v>
+        <v>37.80974728770732</v>
       </c>
       <c r="L67" t="n">
-        <v>1.54</v>
+        <v>1.176780800335431</v>
       </c>
       <c r="M67" t="n">
-        <v>1.04</v>
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>64.8998372188</v>
       </c>
     </row>
     <row r="68">
@@ -3601,35 +3804,38 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>13.9</v>
+        <v>5.728486441062106</v>
       </c>
       <c r="I68" t="n">
-        <v>4.13</v>
+        <v>4.224973190293236</v>
       </c>
       <c r="J68" t="n">
-        <v>0.53</v>
+        <v>0.3645296209106572</v>
       </c>
       <c r="K68" t="n">
-        <v>40.2</v>
+        <v>38.84475790386926</v>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>1.503523325232302</v>
       </c>
       <c r="M68" t="n">
-        <v>7.98</v>
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>8.4599531867</v>
       </c>
     </row>
     <row r="69">
@@ -3648,35 +3854,38 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>17.9</v>
+        <v>4.337890098777239</v>
       </c>
       <c r="I69" t="n">
-        <v>3.45</v>
+        <v>2.567552538527942</v>
       </c>
       <c r="J69" t="n">
-        <v>0.68</v>
+        <v>0.06491371377947049</v>
       </c>
       <c r="K69" t="n">
-        <v>38.9</v>
+        <v>32.77484831358038</v>
       </c>
       <c r="L69" t="n">
-        <v>1.79</v>
+        <v>1.079465365448393</v>
       </c>
       <c r="M69" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>130.9001136338</v>
       </c>
     </row>
     <row r="70">
@@ -3695,35 +3904,38 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.9</v>
+        <v>16.3739779476143</v>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>3.628687295232271</v>
       </c>
       <c r="J70" t="n">
-        <v>0.22</v>
+        <v>0.0985874589528966</v>
       </c>
       <c r="K70" t="n">
-        <v>33.8</v>
+        <v>45.79075365543733</v>
       </c>
       <c r="L70" t="n">
-        <v>1.25</v>
+        <v>1.313052528644854</v>
       </c>
       <c r="M70" t="n">
-        <v>2.4</v>
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1.0655550319</v>
       </c>
     </row>
     <row r="71">
@@ -3742,35 +3954,38 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>20</v>
+        <v>13.81142272984716</v>
       </c>
       <c r="I71" t="n">
-        <v>3.93</v>
+        <v>3.525404260824893</v>
       </c>
       <c r="J71" t="n">
-        <v>0.38</v>
+        <v>0.6788542403204189</v>
       </c>
       <c r="K71" t="n">
-        <v>36.2</v>
+        <v>35.14218120785119</v>
       </c>
       <c r="L71" t="n">
-        <v>1.45</v>
+        <v>1.655713573345692</v>
       </c>
       <c r="M71" t="n">
-        <v>10.9</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>24.0165383863</v>
       </c>
     </row>
     <row r="72">
@@ -3789,35 +4004,38 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4.5</v>
+        <v>17.0011250278064</v>
       </c>
       <c r="I72" t="n">
-        <v>4.05</v>
+        <v>3.359101334440191</v>
       </c>
       <c r="J72" t="n">
-        <v>0.97</v>
+        <v>0.4967344271598957</v>
       </c>
       <c r="K72" t="n">
-        <v>37.8</v>
+        <v>44.58222850253921</v>
       </c>
       <c r="L72" t="n">
-        <v>1.23</v>
+        <v>1.274940243257396</v>
       </c>
       <c r="M72" t="n">
-        <v>10.6</v>
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>15.5836242675</v>
       </c>
     </row>
     <row r="73">
@@ -3836,35 +4054,38 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.4</v>
+        <v>5.990464891226587</v>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>3.914338158933906</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.2566866718446492</v>
       </c>
       <c r="K73" t="n">
-        <v>44.4</v>
+        <v>41.10950164615332</v>
       </c>
       <c r="L73" t="n">
-        <v>1.06</v>
+        <v>1.814501390341014</v>
       </c>
       <c r="M73" t="n">
-        <v>53.7</v>
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>16.1749679985</v>
       </c>
     </row>
     <row r="74">
@@ -3883,35 +4104,38 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>18.6</v>
+        <v>10.65509149033227</v>
       </c>
       <c r="I74" t="n">
-        <v>3.05</v>
+        <v>2.336957962216308</v>
       </c>
       <c r="J74" t="n">
-        <v>0.31</v>
+        <v>0.8280727003977114</v>
       </c>
       <c r="K74" t="n">
-        <v>41.1</v>
+        <v>47.99972053175911</v>
       </c>
       <c r="L74" t="n">
-        <v>1.13</v>
+        <v>1.368012290223699</v>
       </c>
       <c r="M74" t="n">
-        <v>32.7</v>
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>103.0768481204</v>
       </c>
     </row>
     <row r="75">
@@ -3930,35 +4154,38 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>8.699999999999999</v>
+        <v>6.508270648290274</v>
       </c>
       <c r="I75" t="n">
-        <v>4.29</v>
+        <v>4.000902837459329</v>
       </c>
       <c r="J75" t="n">
-        <v>0.01</v>
+        <v>0.4766549680280822</v>
       </c>
       <c r="K75" t="n">
-        <v>35.2</v>
+        <v>47.65594365476986</v>
       </c>
       <c r="L75" t="n">
-        <v>1.59</v>
+        <v>1.437285069219545</v>
       </c>
       <c r="M75" t="n">
-        <v>1.05</v>
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.7718069575</v>
       </c>
     </row>
     <row r="76">
@@ -3977,35 +4204,38 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>10.2</v>
+        <v>11.31153407021058</v>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>3.696558771619143</v>
       </c>
       <c r="J76" t="n">
-        <v>0.18</v>
+        <v>0.7404942934599882</v>
       </c>
       <c r="K76" t="n">
-        <v>45.6</v>
+        <v>48.10181739549456</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>1.238797170869947</v>
       </c>
       <c r="M76" t="n">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>6.6424244323</v>
       </c>
     </row>
     <row r="77">
@@ -4024,35 +4254,38 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>6</v>
+        <v>5.166634530673298</v>
       </c>
       <c r="I77" t="n">
-        <v>4.61</v>
+        <v>3.966343601461431</v>
       </c>
       <c r="J77" t="n">
-        <v>0.84</v>
+        <v>0.1433994237505922</v>
       </c>
       <c r="K77" t="n">
-        <v>49.8</v>
+        <v>34.79938675209277</v>
       </c>
       <c r="L77" t="n">
-        <v>1.38</v>
+        <v>1.100721832380967</v>
       </c>
       <c r="M77" t="n">
-        <v>0.459</v>
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>15.9969472787</v>
       </c>
     </row>
     <row r="78">
@@ -4071,35 +4304,38 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>16.4</v>
+        <v>2.779507429691372</v>
       </c>
       <c r="I78" t="n">
-        <v>2.56</v>
+        <v>2.988782275611591</v>
       </c>
       <c r="J78" t="n">
-        <v>0.63</v>
+        <v>0.8396571690021346</v>
       </c>
       <c r="K78" t="n">
-        <v>46.4</v>
+        <v>49.54227733267598</v>
       </c>
       <c r="L78" t="n">
-        <v>1.48</v>
+        <v>1.761578497767251</v>
       </c>
       <c r="M78" t="n">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>55.0264002787</v>
       </c>
     </row>
     <row r="79">
@@ -4118,35 +4354,38 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9</v>
+        <v>8.998016907853696</v>
       </c>
       <c r="I79" t="n">
-        <v>2.02</v>
+        <v>4.472485423087429</v>
       </c>
       <c r="J79" t="n">
-        <v>0.5</v>
+        <v>0.07870348471256769</v>
       </c>
       <c r="K79" t="n">
-        <v>34.2</v>
+        <v>39.71949527279703</v>
       </c>
       <c r="L79" t="n">
-        <v>1.33</v>
+        <v>1.122441513193543</v>
       </c>
       <c r="M79" t="n">
-        <v>248</v>
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.7544342894</v>
       </c>
     </row>
     <row r="80">
@@ -4165,35 +4404,38 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15.7</v>
+        <v>5.449657448703999</v>
       </c>
       <c r="I80" t="n">
-        <v>3.21</v>
+        <v>2.385159800761087</v>
       </c>
       <c r="J80" t="n">
-        <v>0.55</v>
+        <v>0.6592779449185409</v>
       </c>
       <c r="K80" t="n">
-        <v>43.7</v>
+        <v>33.01491244424255</v>
       </c>
       <c r="L80" t="n">
-        <v>1.68</v>
+        <v>1.910841059250581</v>
       </c>
       <c r="M80" t="n">
-        <v>28.5</v>
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>269.6707926751</v>
       </c>
     </row>
     <row r="81">
@@ -4212,35 +4454,38 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>6.1</v>
+        <v>16.53089719254019</v>
       </c>
       <c r="I81" t="n">
-        <v>2.38</v>
+        <v>2.853758675485683</v>
       </c>
       <c r="J81" t="n">
-        <v>0.71</v>
+        <v>0.2113567638387285</v>
       </c>
       <c r="K81" t="n">
-        <v>47.3</v>
+        <v>33.56783025509031</v>
       </c>
       <c r="L81" t="n">
-        <v>1.9</v>
+        <v>1.846076919190478</v>
       </c>
       <c r="M81" t="n">
-        <v>213</v>
+        <v>1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>114.2498878306</v>
       </c>
     </row>
   </sheetData>
